--- a/stories/arbres/ATOM-SAN.MOV.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kilian a joué un peu dans le salon. Ses jambes ont encore envie de bouger. Papa dit : on va dehors. Ils mettent les chaussures près de la porte. Ils prennent le cerceau bleu. Ils vont au pré avec papa. Dehors, l'air sent l'herbe. Les oiseaux chantent. Kilian court sur l'herbe. Papa reste près de lui. Kilian fait tourner le cerceau. Papa tapote des mains. Kilian dit : je joue dehors, avec un adulte. Papa sourit. Ils jouent un moment. Kilian sent son corps content. Puis ils rentrent ensemble. Kilian a bougé. Papa était là.</t>
+          <t>Kilian a joué un peu dans le salon. Ses jambes ont encore envie de bouger. On va dehors. Ils mettent les chaussures près de la porte. Ils prennent le cerceau bleu. Ils vont au pré avec papa. Dehors, l'air sent l'herbe. Les oiseaux chantent. Kilian court sur l'herbe. Papa reste près de lui. Kilian fait tourner le cerceau. Papa tapote des mains. Je joue dehors, avec un adulte. Papa sourit. Ils jouent un moment. Kilian sent son corps content. Puis ils rentrent ensemble. Kilian a bougé. Papa était là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kilian a joué un peu dans le salon. Ses jambes ont encore envie de bouger.
+papa|On va dehors.
+narrateur|Ils mettent les chaussures près de la porte. Ils prennent le cerceau bleu. Ils vont au pré avec papa. Dehors, l'air sent l'herbe. Les oiseaux chantent. Kilian court sur l'herbe. Papa reste près de lui. Kilian fait tourner le cerceau. Papa tapote des mains.
+enfant-m|Je joue dehors, avec un adulte. Papa sourit. Ils jouent un moment.
+narrateur|Kilian sent son corps content. Puis ils rentrent ensemble. Kilian a bougé. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Kilian veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kilian a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Kilian boit de l'eau. Il range le cerceau. Merci, dit-il à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Kilian sent son corps content. Puis ils rentrent ensemble. Kilian a bougé. Papa était là.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Kilian veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Kilian a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Kilian boit de l'eau. Il range le cerceau. Merci, dit-il à papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.MOV.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kilian joue dehors au pré</t>
+          <t>Le cerceau bleu dans le pré</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une abeille tape à la vitre. Derrière la haie, le pré est doré. Nino et papa emmènent le cerceau bleu. Ils jouent dehors, avec un adulte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kilian a joué un peu dans le salon. Ses jambes ont encore envie de bouger. On va dehors. Ils mettent les chaussures près de la porte. Ils prennent le cerceau bleu. Ils vont au pré avec papa. Dehors, l'air sent l'herbe. Les oiseaux chantent. Kilian court sur l'herbe. Papa reste près de lui. Kilian fait tourner le cerceau. Papa tapote des mains. Je joue dehors, avec un adulte. Papa sourit. Ils jouent un moment. Kilian sent son corps content. Puis ils rentrent ensemble. Kilian a bougé. Papa était là.</t>
+          <t>Une abeille tape à la vitre. Elle fait un petit bzz. Derrière la haie, le pré est doré. Les herbes hautes bougent au vent. Une clochette tinte, très loin. Le chapeau de paille pend au crochet. Nino vit ici, avec papa. Le cerceau bleu attend près des bottes. Papa, l'abeille tape ! Oui. Elle veut les fleurs. Tu vois le pré, derrière la haie ? Oui. C'est tout jaune. En ce moment, les jambes de Nino gigotent. Elles veulent l'herbe haute. On va dehors, Nino ? Oui, papa. On y va ensemble. On joue dehors, avec un adulte. Ils mettent les chaussures près de la porte. Les semelles sentent encore la terre. Tu as fini tes chaussures ? Oui. Bravo. Papa prend le cerceau bleu. Le plastique est lisse et frais. Il est bleu, papa. Oui. Ton cerceau. Ils ouvrent le petit portail. Le portail fait un grincement doux. Dehors, l'air sent l'herbe chaude. Les oiseaux chantent dans la haie. Ça sent le foin ! Oui. Le pré sent le soleil. Nino court sur l'herbe. Les tiges lui chatouillent les genoux. Papa reste près de lui. Je reste tout près. Nino fait tourner le cerceau. Le cerceau roule, puis tombe. Il fait un petit toc dans l'herbe. Tu le relances ? Oui ! Nino relance le cerceau. Papa tapote dans ses mains. Bien roulé, Nino. Je joue dehors, avec un adulte. Oui. Bravo. Un papillon jaune passe tout bas. Nino le suit de l'œil. Tu le vois, le papillon ? Oui. Il est jaune. Ils jouent un moment. Nino sent son corps content. Ses joues sont chaudes. Tu as assez bougé ? Encore un peu. Encore un tour de cerceau, alors. Le cerceau roule une dernière fois. Il s'arrête près de la haie. On rentre ensemble ? Oui, papa. Nino porte le cerceau. Le portail se referme, tout doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,82 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Kilian a joué un peu dans le salon. Ses jambes ont encore envie de bouger.
-papa|On va dehors.
-narrateur|Ils mettent les chaussures près de la porte. Ils prennent le cerceau bleu. Ils vont au pré avec papa. Dehors, l'air sent l'herbe. Les oiseaux chantent. Kilian court sur l'herbe. Papa reste près de lui. Kilian fait tourner le cerceau. Papa tapote des mains.
-enfant-m|Je joue dehors, avec un adulte. Papa sourit. Ils jouent un moment.
-narrateur|Kilian sent son corps content. Puis ils rentrent ensemble. Kilian a bougé. Papa était là.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une abeille tape à la vitre.
+narrateur|Elle fait un petit bzz.
+narrateur|Derrière la haie, le pré est doré.
+narrateur|Les herbes hautes bougent au vent.
+narrateur|Une clochette tinte, très loin.
+narrateur|Le chapeau de paille pend au crochet.
+narrateur|Nino vit ici, avec papa.
+narrateur|Le cerceau bleu attend près des bottes.
+enfant-m|Papa, l'abeille tape !
+papa|Oui.
+papa|Elle veut les fleurs.
+papa|Tu vois le pré, derrière la haie ?
+enfant-m|Oui.
+enfant-m|C'est tout jaune.
+narrateur|En ce moment, les jambes de Nino gigotent.
+narrateur|Elles veulent l'herbe haute.
+papa|On va dehors, Nino ?
+enfant-m|Oui, papa.
+papa|On y va ensemble.
+papa|On joue dehors, avec un adulte.
+narrateur|Ils mettent les chaussures près de la porte.
+narrateur|Les semelles sentent encore la terre.
+papa|Tu as fini tes chaussures ?
+enfant-m|Oui.
+papa|Bravo.
+narrateur|Papa prend le cerceau bleu.
+narrateur|Le plastique est lisse et frais.
+enfant-m|Il est bleu, papa.
+papa|Oui.
+papa|Ton cerceau.
+narrateur|Ils ouvrent le petit portail.
+narrateur|Le portail fait un grincement doux.
+narrateur|Dehors, l'air sent l'herbe chaude.
+narrateur|Les oiseaux chantent dans la haie.
+enfant-m|Ça sent le foin !
+papa|Oui.
+papa|Le pré sent le soleil.
+narrateur|Nino court sur l'herbe.
+narrateur|Les tiges lui chatouillent les genoux.
+narrateur|Papa reste près de lui.
+papa|Je reste tout près.
+narrateur|Nino fait tourner le cerceau.
+narrateur|Le cerceau roule, puis tombe.
+narrateur|Il fait un petit toc dans l'herbe.
+papa|Tu le relances ?
+enfant-m|Oui !
+narrateur|Nino relance le cerceau.
+narrateur|Papa tapote dans ses mains.
+papa|Bien roulé, Nino.
+enfant-m|Je joue dehors, avec un adulte.
+papa|Oui.
+papa|Bravo.
+narrateur|Un papillon jaune passe tout bas.
+narrateur|Nino le suit de l'œil.
+papa|Tu le vois, le papillon ?
+enfant-m|Oui.
+enfant-m|Il est jaune.
+narrateur|Ils jouent un moment.
+narrateur|Nino sent son corps content.
+narrateur|Ses joues sont chaudes.
+papa|Tu as assez bougé ?
+enfant-m|Encore un peu.
+papa|Encore un tour de cerceau, alors.
+narrateur|Le cerceau roule une dernière fois.
+narrateur|Il s'arrête près de la haie.
+papa|On rentre ensemble ?
+enfant-m|Oui, papa.
+narrateur|Nino porte le cerceau.
+narrateur|Le portail se referme, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>abeille,cerceau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1429,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Kilian veut bouger. Où joue-t-il ?</t>
+          <t>Nino veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1585,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Kilian veut bouger. Où joue-t-il ?</t>
+          <t>narrateur|Nino veut bouger.
+narrateur|Où joue-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1614,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kilian a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien.</t>
+          <t>Nino a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. Tu as joué dehors, avec un adulte ? Oui, papa. Dehors. Bravo, Nino. Tu as fait du bon travail. Le cerceau bleu repose près des bottes. Il garde un brin d'herbe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1758,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Kilian a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien.</t>
+          <t>narrateur|Nino a joué dehors.
+narrateur|Papa, un adulte, était avec lui.
+narrateur|Le corps a bougé.
+papa|Tu as joué dehors, avec un adulte ?
+enfant-m|Oui, papa.
+enfant-m|Dehors.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Le cerceau bleu repose près des bottes.
+narrateur|Il garde un brin d'herbe.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1795,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Kilian boit de l'eau. Il range le cerceau. Merci, dit-il à papa.</t>
+          <t>Sur la table, un verre d'eau attend. Tu bois un peu d'eau ? Nino boit une gorgée. L'eau est fraîche. Merci, papa. Tu ranges le cerceau ? Nino accroche le cerceau au clou. Tu as fini de ranger ? Oui. Bravo. L'abeille s'éloigne vers les fleurs. Le pré reste doré, derrière la haie.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1836,7 +1931,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Kilian boit de l'eau. Il range le cerceau. Merci, dit-il à papa.</t>
+          <t>narrateur|Sur la table, un verre d'eau attend.
+papa|Tu bois un peu d'eau ?
+narrateur|Nino boit une gorgée.
+narrateur|L'eau est fraîche.
+enfant-m|Merci, papa.
+papa|Tu ranges le cerceau ?
+narrateur|Nino accroche le cerceau au clou.
+papa|Tu as fini de ranger ?
+enfant-m|Oui.
+papa|Bravo.
+narrateur|L'abeille s'éloigne vers les fleurs.
+narrateur|Le pré reste doré, derrière la haie.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1864,7 +1970,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai fait tourner le cerceau. J'ai joué dehors. Avec un adulte. Bravo. C'est du bon travail. Le chapeau de paille pend encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2004,7 +2110,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai fait tourner le cerceau.
+enfant-m|J'ai joué dehors.
+papa|Avec un adulte.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Le chapeau de paille pend encore.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2026,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2176,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-06.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kilian a joué un peu dans le salon. Ses jambes ont encore envie de bouger. Papa dit : on va &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Ils mettent les chaussures près de la porte. Ils prennent le cerceau bleu. Ils vont au pré avec papa. Dehors, l'air sent l'herbe. Les oiseaux chantent. Kilian court sur l'herbe. Papa reste près de lui. Kilian fait tourner le cerceau. Papa tapote des mains. Kilian dit : je joue dehors, avec un adulte. Papa sourit. Ils jouent un moment. Kilian sent son corps content. Puis ils rentrent ensemble. Kilian a bougé. Papa était là.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une abeille tape à la vitre. Elle fait un petit bzz. Derrière la haie, le pré est doré. Les herbes hautes bougent au vent. Une clochette tinte, très loin. Le chapeau de paille pend au crochet. Nino vit ici, avec papa. Le cerceau bleu attend près des bottes. Papa, l'abeille tape ! Oui. Elle veut les fleurs. Tu vois le pré, derrière la haie ? Oui. C'est tout jaune. En ce moment, les jambes de Nino gigotent. Elles veulent l'herbe haute. On va dehors, Nino ? Oui, papa. On y va ensemble. On joue dehors, avec un adulte. Ils mettent les chaussures près de la porte. Les semelles sentent encore la terre. Tu as fini tes chaussures ? Oui. Bravo. Papa prend le cerceau bleu. Le plastique est lisse et frais. Il est bleu, papa. Oui. Ton cerceau. Ils ouvrent le petit portail. Le portail fait un grincement doux. Dehors, l'air sent l'herbe chaude. Les oiseaux chantent dans la haie. Ça sent le foin ! Oui. Le pré sent le soleil. Nino court sur l'herbe. Les tiges lui chatouillent les genoux. Papa reste près de lui. Je reste tout près. Nino fait tourner le cerceau. Le cerceau roule, puis tombe. Il fait un petit toc dans l'herbe. Tu le relances ? Oui ! Nino relance le cerceau. Papa tapote dans ses mains. Bien roulé, Nino. Je joue dehors, avec un adulte. Oui. Bravo. Un papillon jaune passe tout bas. Nino le suit de l'œil. Tu le vois, le papillon ? Oui. Il est jaune. Ils jouent un moment. Nino sent son corps content. Ses joues sont chaudes. Tu as assez bougé ? Encore un peu. Encore un tour de cerceau, alors. Le cerceau roule une dernière fois. Il s'arrête près de la haie. On rentre ensemble ? Oui, papa. Nino porte le cerceau. Le portail se referme, tout doux.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Kilian veut bouger. Où joue-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino veut bouger. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1589,7 +1589,6 @@
 narrateur|Où joue-t-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1614,12 +1613,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. Tu as joué dehors, avec un adulte ? Oui, papa. Dehors. Bravo, Nino. Tu as fait du bon travail. Le cerceau bleu repose près des bottes. Il garde un brin d'herbe.</t>
+          <t>Nino a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. Tu as joué dehors, avec un adulte ? Oui, papa. Dehors. Bravo, Nino. Le cerceau bleu repose près des bottes. Il garde un brin d'herbe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kilian a joué &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Papa, un adulte, était avec lui. Le corps a bougé. C'est bien.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a joué dehors. Papa, un adulte, était avec lui. Le corps a bougé. Tu as joué dehors, avec un adulte ? Oui, papa. Dehors. Bravo, Nino. Le cerceau bleu repose près des bottes. Il garde un brin d'herbe.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1765,12 +1764,10 @@
 enfant-m|Oui, papa.
 enfant-m|Dehors.
 papa|Bravo, Nino.
-papa|Tu as fait du bon travail.
 narrateur|Le cerceau bleu repose près des bottes.
 narrateur|Il garde un brin d'herbe.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1800,7 +1797,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kilian boit de l'eau. Il range le cerceau. Merci, dit-il à papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur la table, un verre d'eau attend. Tu bois un peu d'eau ? Nino boit une gorgée. L'eau est fraîche. Merci, papa. Tu ranges le cerceau ? Nino accroche le cerceau au clou. Tu as fini de ranger ? Oui. Bravo. L'abeille s'éloigne vers les fleurs. Le pré reste doré, derrière la haie.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1945,7 +1942,6 @@
 narrateur|Le pré reste doré, derrière la haie.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1970,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai fait tourner le cerceau. J'ai joué dehors. Avec un adulte. Bravo. C'est du bon travail. Le chapeau de paille pend encore. L'histoire est finie.</t>
+          <t>J'ai fait tourner le cerceau. J'ai joué dehors. Avec un adulte. Bravo. Le chapeau de paille pend encore.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai fait tourner le cerceau. J'ai joué dehors. Avec un adulte. Bravo. Le chapeau de paille pend encore.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2114,12 +2110,9 @@
 enfant-m|J'ai joué dehors.
 papa|Avec un adulte.
 papa|Bravo.
-papa|C'est du bon travail.
-narrateur|Le chapeau de paille pend encore.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le chapeau de paille pend encore.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2138,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2183,6 +2176,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-06.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-06.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pré près de la maison</t>
+          <t>pré près de la maison, haie, cerceau bleu</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kilian, papa</t>
+          <t>Nino, papa</t>
         </is>
       </c>
     </row>
